--- a/data/trans_orig/DC-Edad-trans_orig.xlsx
+++ b/data/trans_orig/DC-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico en 2007</t>
+          <t>Población con dolor crónico en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32361</t>
+          <t>31801</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83279</t>
+          <t>82219</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>116846</t>
+          <t>118616</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100643</t>
+          <t>101905</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141346</t>
+          <t>141957</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>461703</t>
+          <t>462263</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>480545</t>
+          <t>480086</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>350643</t>
+          <t>348873</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>384210</t>
+          <t>385270</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>820207</t>
+          <t>819596</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>860910</t>
+          <t>859648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,4%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49487</t>
+          <t>50282</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80659</t>
+          <t>83116</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>134754</t>
+          <t>133757</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>176207</t>
+          <t>176454</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>191573</t>
+          <t>193720</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>245061</t>
+          <t>250335</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>654830</t>
+          <t>652373</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>686002</t>
+          <t>685207</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>449287</t>
+          <t>449040</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>490740</t>
+          <t>491737</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1115921</t>
+          <t>1110647</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1169409</t>
+          <t>1167262</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,77%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83126</t>
+          <t>82152</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>118923</t>
+          <t>116457</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>134887</t>
+          <t>136439</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>178272</t>
+          <t>182809</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>225528</t>
+          <t>226400</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>282656</t>
+          <t>281195</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519745</t>
+          <t>522211</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>555542</t>
+          <t>556516</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>511472</t>
+          <t>506935</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>554857</t>
+          <t>553305</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1045756</t>
+          <t>1047217</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1102884</t>
+          <t>1102012</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,96%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91571</t>
+          <t>93071</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127504</t>
+          <t>128576</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>123382</t>
+          <t>122771</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165133</t>
+          <t>161943</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>222714</t>
+          <t>223931</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>282080</t>
+          <t>279051</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>391643</t>
+          <t>390571</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>427576</t>
+          <t>426076</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>350509</t>
+          <t>353699</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>392260</t>
+          <t>392871</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>752709</t>
+          <t>755738</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>812075</t>
+          <t>810858</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,36%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>104218</t>
+          <t>104971</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>142541</t>
+          <t>140586</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>107284</t>
+          <t>106552</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142892</t>
+          <t>142411</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>222612</t>
+          <t>224825</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>273497</t>
+          <t>277674</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>35,12%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>244169</t>
+          <t>246124</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>282492</t>
+          <t>281739</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>261094</t>
+          <t>261575</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>296702</t>
+          <t>297434</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>517199</t>
+          <t>513022</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>568084</t>
+          <t>565871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,57%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66197</t>
+          <t>65405</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>94878</t>
+          <t>95731</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>126487</t>
+          <t>124160</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>159413</t>
+          <t>159033</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>198302</t>
+          <t>198809</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>243433</t>
+          <t>245788</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>197705</t>
+          <t>196852</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>226386</t>
+          <t>227178</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>183521</t>
+          <t>183901</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>216447</t>
+          <t>218774</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>392084</t>
+          <t>389729</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>437215</t>
+          <t>436708</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,72%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63766</t>
+          <t>64169</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>91790</t>
+          <t>91406</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>106755</t>
+          <t>106481</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>142351</t>
+          <t>143840</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>177855</t>
+          <t>178881</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>224554</t>
+          <t>223356</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,07%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118093</t>
+          <t>118477</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>146117</t>
+          <t>145714</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>191557</t>
+          <t>190068</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>227153</t>
+          <t>227427</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>319237</t>
+          <t>320435</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>365936</t>
+          <t>364910</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,1%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>534641</t>
+          <t>532336</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>619071</t>
+          <t>618642</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>893553</t>
+          <t>887963</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>999137</t>
+          <t>995197</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1444561</t>
+          <t>1447744</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1583231</t>
+          <t>1578929</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2657472</t>
+          <t>2657901</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2741902</t>
+          <t>2744207</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2380060</t>
+          <t>2384000</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2485644</t>
+          <t>2491234</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5072510</t>
+          <t>5076812</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5211180</t>
+          <t>5207997</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,25%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico en 2012</t>
+          <t>Población con dolor crónico en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27886</t>
+          <t>27213</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54355</t>
+          <t>53154</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>85576</t>
+          <t>83317</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68925</t>
+          <t>67847</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104146</t>
+          <t>103482</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>426260</t>
+          <t>426933</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>444277</t>
+          <t>443630</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>344654</t>
+          <t>346913</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>375875</t>
+          <t>377076</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>780230</t>
+          <t>780894</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>815451</t>
+          <t>816529</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,33%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27657</t>
+          <t>27634</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53876</t>
+          <t>52549</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71013</t>
+          <t>72197</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106084</t>
+          <t>109449</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107501</t>
+          <t>107241</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150685</t>
+          <t>151372</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>633211</t>
+          <t>634538</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>659430</t>
+          <t>659453</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>504171</t>
+          <t>500806</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>539242</t>
+          <t>538058</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1146657</t>
+          <t>1145970</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1189841</t>
+          <t>1190101</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38118</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65662</t>
+          <t>65921</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>123733</t>
+          <t>122353</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>167035</t>
+          <t>165591</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169011</t>
+          <t>169584</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>220429</t>
+          <t>222318</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>616201</t>
+          <t>615942</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>643745</t>
+          <t>643759</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>543815</t>
+          <t>545259</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>587117</t>
+          <t>588497</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1172283</t>
+          <t>1170394</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1223701</t>
+          <t>1223128</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,82%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45801</t>
+          <t>47040</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74987</t>
+          <t>78934</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109763</t>
+          <t>108624</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>151730</t>
+          <t>151512</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>163992</t>
+          <t>163123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>216981</t>
+          <t>217538</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>539630</t>
+          <t>535683</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>568816</t>
+          <t>567577</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>464469</t>
+          <t>464687</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>506436</t>
+          <t>507575</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1013835</t>
+          <t>1013278</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1066824</t>
+          <t>1067693</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,75%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44223</t>
+          <t>42974</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73828</t>
+          <t>72851</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>109386</t>
+          <t>110408</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150280</t>
+          <t>150062</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>164019</t>
+          <t>163549</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>216136</t>
+          <t>212586</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>355601</t>
+          <t>356578</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>385206</t>
+          <t>386455</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>297520</t>
+          <t>297738</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>338414</t>
+          <t>337392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>661093</t>
+          <t>664643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>713210</t>
+          <t>713680</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,36%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50263</t>
+          <t>49961</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79962</t>
+          <t>80231</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>103858</t>
+          <t>105155</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>139608</t>
+          <t>141218</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>162718</t>
+          <t>163716</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>209185</t>
+          <t>210806</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>229824</t>
+          <t>229555</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259523</t>
+          <t>259825</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>214388</t>
+          <t>212778</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250138</t>
+          <t>248841</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>454597</t>
+          <t>452976</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>501064</t>
+          <t>500066</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,34%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51463</t>
+          <t>50434</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>80913</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>146795</t>
+          <t>147522</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>186697</t>
+          <t>188713</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>204156</t>
+          <t>207244</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>254244</t>
+          <t>258666</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>170657</t>
+          <t>168938</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>198388</t>
+          <t>199417</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>202282</t>
+          <t>200266</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>242184</t>
+          <t>241457</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>384586</t>
+          <t>380164</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>434674</t>
+          <t>431586</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>67,56%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>322100</t>
+          <t>321648</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>392294</t>
+          <t>393929</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>798128</t>
+          <t>795179</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>901736</t>
+          <t>899494</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1134634</t>
+          <t>1141083</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1266868</t>
+          <t>1274004</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3034485</t>
+          <t>3032850</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3104679</t>
+          <t>3105131</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2656573</t>
+          <t>2658815</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2760181</t>
+          <t>2763130</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5718220</t>
+          <t>5711084</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5850454</t>
+          <t>5844005</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico en 2016</t>
+          <t>Población con dolor crónico en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2173</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12470</t>
+          <t>13032</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29131</t>
+          <t>27876</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51618</t>
+          <t>51314</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,47 +6741,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>12,97%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>45070</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>33475</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>60005</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>7,36%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>45070</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>33851</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>58979</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406993</t>
+          <t>406431</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>417399</t>
+          <t>417290</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>344137</t>
+          <t>344441</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>366624</t>
+          <t>367879</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,47 +6854,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>92,96%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>770148</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>755213</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>781743</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>94,47%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>92,64%</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>752</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>770148</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>756239</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>781367</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>94,47%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>92,77%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13346</t>
+          <t>12967</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33896</t>
+          <t>33892</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61440</t>
+          <t>61917</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94385</t>
+          <t>94688</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78973</t>
+          <t>81060</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116794</t>
+          <t>119632</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>556600</t>
+          <t>556604</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>577150</t>
+          <t>577529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>469159</t>
+          <t>468856</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502104</t>
+          <t>501627</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1037246</t>
+          <t>1034408</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1075067</t>
+          <t>1072980</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,98%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34513</t>
+          <t>35636</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63176</t>
+          <t>63329</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65330</t>
+          <t>62769</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97813</t>
+          <t>98048</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>106278</t>
+          <t>108601</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149867</t>
+          <t>153422</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>605921</t>
+          <t>605768</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>634584</t>
+          <t>633461</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>563573</t>
+          <t>563338</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>596056</t>
+          <t>598617</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1180616</t>
+          <t>1177061</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1224205</t>
+          <t>1221882</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47742</t>
+          <t>49709</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80439</t>
+          <t>82106</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91153</t>
+          <t>92479</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131666</t>
+          <t>129438</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149725</t>
+          <t>149997</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>199350</t>
+          <t>200809</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>565609</t>
+          <t>563942</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>598306</t>
+          <t>596339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>517411</t>
+          <t>519639</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>557924</t>
+          <t>556598</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1095775</t>
+          <t>1094316</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1145400</t>
+          <t>1145128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,42%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57874</t>
+          <t>57566</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90075</t>
+          <t>89464</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>104113</t>
+          <t>105539</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>143519</t>
+          <t>142708</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>170159</t>
+          <t>171626</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>223076</t>
+          <t>223551</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>387843</t>
+          <t>388454</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>420044</t>
+          <t>420352</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>353330</t>
+          <t>354141</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>392736</t>
+          <t>391310</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>751691</t>
+          <t>751216</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>804608</t>
+          <t>803141</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40070</t>
+          <t>39135</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67660</t>
+          <t>65258</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>76895</t>
+          <t>76993</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>108571</t>
+          <t>112309</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>121249</t>
+          <t>122491</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>166458</t>
+          <t>167114</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>266670</t>
+          <t>269072</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>294260</t>
+          <t>295195</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>269191</t>
+          <t>265453</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>300867</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>545634</t>
+          <t>544978</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>590843</t>
+          <t>589601</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,8%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46803</t>
+          <t>46595</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71115</t>
+          <t>70715</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>111724</t>
+          <t>111060</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>151192</t>
+          <t>151422</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>163170</t>
+          <t>164037</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>213723</t>
+          <t>214309</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,61%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>185883</t>
+          <t>186283</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>210195</t>
+          <t>210403</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>248977</t>
+          <t>248747</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>288445</t>
+          <t>289109</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>443444</t>
+          <t>442858</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>493997</t>
+          <t>493130</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,04%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>286053</t>
+          <t>287743</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>360552</t>
+          <t>357414</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>600473</t>
+          <t>606242</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>694991</t>
+          <t>705030</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>911753</t>
+          <t>915013</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1030591</t>
+          <t>1032720</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3033798</t>
+          <t>3036936</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3108297</t>
+          <t>3106607</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2849551</t>
+          <t>2839512</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2944069</t>
+          <t>2938300</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5908301</t>
+          <t>5906172</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6027139</t>
+          <t>6023879</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,81%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico en 2023</t>
+          <t>Población con dolor crónico en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15927</t>
+          <t>15509</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58463</t>
+          <t>55506</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57404</t>
+          <t>57839</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97771</t>
+          <t>96444</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79700</t>
+          <t>81909</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138417</t>
+          <t>139183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>341524</t>
+          <t>344481</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>384060</t>
+          <t>384478</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215429</t>
+          <t>216756</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>255796</t>
+          <t>255361</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>574770</t>
+          <t>574004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>633487</t>
+          <t>631278</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,52%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28506</t>
+          <t>29543</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59522</t>
+          <t>59021</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>127879</t>
+          <t>131363</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313067</t>
+          <t>322075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163947</t>
+          <t>165130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>402653</t>
+          <t>407097</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,51%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>364025</t>
+          <t>364526</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>395041</t>
+          <t>394004</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>199026</t>
+          <t>190018</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>384214</t>
+          <t>380730</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>532987</t>
+          <t>528543</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>771693</t>
+          <t>770510</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,35%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62140</t>
+          <t>62051</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98188</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127128</t>
+          <t>123024</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>190302</t>
+          <t>188699</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>202031</t>
+          <t>206969</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>270808</t>
+          <t>269040</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>438150</t>
+          <t>440826</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>474198</t>
+          <t>474287</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>401700</t>
+          <t>403303</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>464874</t>
+          <t>468978</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>857532</t>
+          <t>859300</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>926309</t>
+          <t>921371</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,66%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64750</t>
+          <t>68203</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>221531</t>
+          <t>221758</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>214847</t>
+          <t>218369</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>277139</t>
+          <t>279185</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>231602</t>
+          <t>259605</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>493771</t>
+          <t>498870</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>666255</t>
+          <t>666028</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>823036</t>
+          <t>819583</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>435742</t>
+          <t>433696</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>498034</t>
+          <t>494512</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1106896</t>
+          <t>1101797</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1369065</t>
+          <t>1341062</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>83,78%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>144911</t>
+          <t>147251</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>186518</t>
+          <t>187554</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>222261</t>
+          <t>223517</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>257318</t>
+          <t>257382</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>380190</t>
+          <t>378992</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>434830</t>
+          <t>436479</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,35%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>374716</t>
+          <t>373680</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>416323</t>
+          <t>413983</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>290587</t>
+          <t>290523</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>325644</t>
+          <t>324388</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>674309</t>
+          <t>672660</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>728949</t>
+          <t>730147</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,83%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>95680</t>
+          <t>96093</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124204</t>
+          <t>123490</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>283098</t>
+          <t>284612</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>519179</t>
+          <t>512487</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>376617</t>
+          <t>375525</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>724139</t>
+          <t>725401</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>243961</t>
+          <t>244675</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>272485</t>
+          <t>272072</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>89189</t>
+          <t>95881</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>325270</t>
+          <t>323756</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>252394</t>
+          <t>251132</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>599916</t>
+          <t>601008</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,55%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105898</t>
+          <t>105330</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>130329</t>
+          <t>130219</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>237069</t>
+          <t>236937</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>266385</t>
+          <t>266323</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>347759</t>
+          <t>349451</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>387110</t>
+          <t>387659</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,71%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>152430</t>
+          <t>152540</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>176861</t>
+          <t>177429</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>159446</t>
+          <t>159508</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>188762</t>
+          <t>188894</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>321480</t>
+          <t>320931</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>360831</t>
+          <t>359139</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,68%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>558646</t>
+          <t>541691</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>774040</t>
+          <t>774077</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1402061</t>
+          <t>1405779</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1966429</t>
+          <t>1954309</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2040610</t>
+          <t>2046408</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2786276</t>
+          <t>2721471</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2685777</t>
+          <t>2685740</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2901171</t>
+          <t>2918126</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1745851</t>
+          <t>1757971</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2310219</t>
+          <t>2306501</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4385821</t>
+          <t>4450626</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5131487</t>
+          <t>5125689</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/DC-Edad-trans_orig.xlsx
+++ b/data/trans_orig/DC-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13978</t>
+          <t>13337</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31801</t>
+          <t>31815</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82219</t>
+          <t>82757</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118616</t>
+          <t>116974</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101905</t>
+          <t>100289</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141957</t>
+          <t>139331</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>462263</t>
+          <t>462249</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>480086</t>
+          <t>480727</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>348873</t>
+          <t>350515</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>385270</t>
+          <t>384732</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>819596</t>
+          <t>822222</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>859648</t>
+          <t>861264</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,57%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50282</t>
+          <t>50658</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83116</t>
+          <t>80704</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>133757</t>
+          <t>134436</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>176454</t>
+          <t>179825</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>193720</t>
+          <t>194513</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>250335</t>
+          <t>249353</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>652373</t>
+          <t>654785</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>685207</t>
+          <t>684831</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>449040</t>
+          <t>445669</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491737</t>
+          <t>491058</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1110647</t>
+          <t>1111629</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1167262</t>
+          <t>1166469</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82152</t>
+          <t>82424</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116457</t>
+          <t>118929</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>136439</t>
+          <t>134593</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>182809</t>
+          <t>180454</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>226400</t>
+          <t>225979</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>281195</t>
+          <t>285688</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522211</t>
+          <t>519739</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>556516</t>
+          <t>556244</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>506935</t>
+          <t>509290</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>553305</t>
+          <t>555151</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1047217</t>
+          <t>1042724</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1102012</t>
+          <t>1102433</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93071</t>
+          <t>91801</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128576</t>
+          <t>128852</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>122771</t>
+          <t>121741</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>161943</t>
+          <t>161757</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>223931</t>
+          <t>226418</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>279051</t>
+          <t>280755</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>390571</t>
+          <t>390295</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>426076</t>
+          <t>427346</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>353699</t>
+          <t>353885</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>392871</t>
+          <t>393901</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>755738</t>
+          <t>754034</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>810858</t>
+          <t>808371</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,12%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>104971</t>
+          <t>106790</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140586</t>
+          <t>143737</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>106552</t>
+          <t>105690</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142411</t>
+          <t>144321</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>224825</t>
+          <t>223601</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>277674</t>
+          <t>275698</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>246124</t>
+          <t>242973</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>281739</t>
+          <t>279920</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>261575</t>
+          <t>259665</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>297434</t>
+          <t>298296</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>513022</t>
+          <t>514998</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>565871</t>
+          <t>567095</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,72%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65405</t>
+          <t>65885</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95731</t>
+          <t>95140</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>124160</t>
+          <t>125075</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>159033</t>
+          <t>157137</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>198809</t>
+          <t>200966</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>245788</t>
+          <t>245339</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>196852</t>
+          <t>197443</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>227178</t>
+          <t>226698</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>183901</t>
+          <t>185797</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>218774</t>
+          <t>217859</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>389729</t>
+          <t>390178</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>436708</t>
+          <t>434551</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,38%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64169</t>
+          <t>65542</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>91406</t>
+          <t>91045</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>106481</t>
+          <t>107618</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>143840</t>
+          <t>143408</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>178881</t>
+          <t>179259</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>223356</t>
+          <t>225843</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118477</t>
+          <t>118838</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>145714</t>
+          <t>144341</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>190068</t>
+          <t>190500</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>227427</t>
+          <t>226290</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>320435</t>
+          <t>317948</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>364910</t>
+          <t>364532</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,04%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>532336</t>
+          <t>533223</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>618642</t>
+          <t>622922</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>887963</t>
+          <t>892353</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>995197</t>
+          <t>999527</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1447744</t>
+          <t>1439946</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1578929</t>
+          <t>1579800</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2657901</t>
+          <t>2653621</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2744207</t>
+          <t>2743320</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2384000</t>
+          <t>2379670</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2491234</t>
+          <t>2486844</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5076812</t>
+          <t>5075941</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5207997</t>
+          <t>5215795</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,37%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>10281</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27213</t>
+          <t>27350</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53154</t>
+          <t>54373</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83317</t>
+          <t>85163</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67847</t>
+          <t>68246</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103482</t>
+          <t>103257</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>426933</t>
+          <t>426796</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>443630</t>
+          <t>443865</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>346913</t>
+          <t>345067</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>377076</t>
+          <t>375857</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>780894</t>
+          <t>781119</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>816529</t>
+          <t>816130</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27634</t>
+          <t>28832</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52549</t>
+          <t>52331</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72197</t>
+          <t>72742</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109449</t>
+          <t>111018</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107241</t>
+          <t>108325</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>151372</t>
+          <t>152155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>634538</t>
+          <t>634756</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>659453</t>
+          <t>658255</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500806</t>
+          <t>499237</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>538058</t>
+          <t>537513</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1145970</t>
+          <t>1145187</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1190101</t>
+          <t>1189017</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38104</t>
+          <t>37273</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65921</t>
+          <t>65926</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>122353</t>
+          <t>121218</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165591</t>
+          <t>167308</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169584</t>
+          <t>169613</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>222318</t>
+          <t>223657</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>615942</t>
+          <t>615937</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>643759</t>
+          <t>644590</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>545259</t>
+          <t>543542</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>588497</t>
+          <t>589632</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1170394</t>
+          <t>1169055</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1223128</t>
+          <t>1223099</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47040</t>
+          <t>45781</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78934</t>
+          <t>76815</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108624</t>
+          <t>108332</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>151512</t>
+          <t>152250</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>163123</t>
+          <t>164190</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>217538</t>
+          <t>215306</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>535683</t>
+          <t>537802</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>567577</t>
+          <t>568836</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>464687</t>
+          <t>463949</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>507575</t>
+          <t>507867</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1013278</t>
+          <t>1015510</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1067693</t>
+          <t>1066626</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,66%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42974</t>
+          <t>44504</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72851</t>
+          <t>71311</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110408</t>
+          <t>109911</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150062</t>
+          <t>149476</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>163549</t>
+          <t>163635</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>212586</t>
+          <t>211846</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>356578</t>
+          <t>358118</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>386455</t>
+          <t>384925</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>297738</t>
+          <t>298324</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>337392</t>
+          <t>337889</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>664643</t>
+          <t>665383</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>713680</t>
+          <t>713594</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,35%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49961</t>
+          <t>51547</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80231</t>
+          <t>79525</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>105155</t>
+          <t>105281</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>141218</t>
+          <t>139670</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>163716</t>
+          <t>164346</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>210806</t>
+          <t>210801</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>229555</t>
+          <t>230261</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259825</t>
+          <t>258239</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>212778</t>
+          <t>214326</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>248841</t>
+          <t>248715</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>452976</t>
+          <t>452981</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>500066</t>
+          <t>499436</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,24%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50434</t>
+          <t>49973</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>80913</t>
+          <t>78627</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>147522</t>
+          <t>146526</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>188713</t>
+          <t>187907</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>207244</t>
+          <t>206472</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>258666</t>
+          <t>255895</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,06%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>168938</t>
+          <t>171224</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>199417</t>
+          <t>199878</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>200266</t>
+          <t>201072</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>241457</t>
+          <t>242453</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>380164</t>
+          <t>382935</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>431586</t>
+          <t>432358</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,68%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>321648</t>
+          <t>315704</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>393929</t>
+          <t>391960</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>795179</t>
+          <t>795910</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>899494</t>
+          <t>895993</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1141083</t>
+          <t>1135931</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1274004</t>
+          <t>1268886</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3032850</t>
+          <t>3034819</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3105131</t>
+          <t>3111075</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2658815</t>
+          <t>2662316</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2763130</t>
+          <t>2762399</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5711084</t>
+          <t>5716202</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5844005</t>
+          <t>5849157</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,74%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2173</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13032</t>
+          <t>13001</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27876</t>
+          <t>29003</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51314</t>
+          <t>53315</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33475</t>
+          <t>33907</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60005</t>
+          <t>60042</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406431</t>
+          <t>406462</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>417290</t>
+          <t>417222</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>344441</t>
+          <t>342440</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>367879</t>
+          <t>366752</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>755213</t>
+          <t>755176</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>781743</t>
+          <t>781311</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12967</t>
+          <t>13476</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33892</t>
+          <t>33983</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61917</t>
+          <t>62400</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94688</t>
+          <t>94037</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81060</t>
+          <t>80743</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119632</t>
+          <t>119371</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>556604</t>
+          <t>556513</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>577529</t>
+          <t>577020</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>468856</t>
+          <t>469507</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>501627</t>
+          <t>501144</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1034408</t>
+          <t>1034669</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1072980</t>
+          <t>1073297</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35636</t>
+          <t>34779</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63329</t>
+          <t>62653</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62769</t>
+          <t>66024</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98048</t>
+          <t>100309</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108601</t>
+          <t>107759</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>153422</t>
+          <t>154256</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>605768</t>
+          <t>606444</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>633461</t>
+          <t>634318</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>563338</t>
+          <t>561077</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>598617</t>
+          <t>595362</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1177061</t>
+          <t>1176227</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1221882</t>
+          <t>1222724</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,9%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49709</t>
+          <t>49428</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82106</t>
+          <t>80111</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>92479</t>
+          <t>91281</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129438</t>
+          <t>128759</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149997</t>
+          <t>150733</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>200809</t>
+          <t>200971</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>563942</t>
+          <t>565937</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>596339</t>
+          <t>596620</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>519639</t>
+          <t>520318</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>556598</t>
+          <t>557796</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1094316</t>
+          <t>1094154</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1145128</t>
+          <t>1144392</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,36%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57566</t>
+          <t>57179</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89464</t>
+          <t>90995</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105539</t>
+          <t>102848</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142708</t>
+          <t>144525</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>171626</t>
+          <t>169772</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>223551</t>
+          <t>222482</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>388454</t>
+          <t>386923</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>420352</t>
+          <t>420739</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>354141</t>
+          <t>352324</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>391310</t>
+          <t>394001</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>751216</t>
+          <t>752285</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>803141</t>
+          <t>804995</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,58%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39135</t>
+          <t>39163</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>66181</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>76993</t>
+          <t>75492</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112309</t>
+          <t>109433</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>122491</t>
+          <t>124909</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>167114</t>
+          <t>165378</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,22%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>269072</t>
+          <t>268149</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>295195</t>
+          <t>295167</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>265453</t>
+          <t>268329</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>300769</t>
+          <t>302270</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>544978</t>
+          <t>546714</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>589601</t>
+          <t>587183</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,46%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46595</t>
+          <t>45680</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70715</t>
+          <t>71277</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>111060</t>
+          <t>108205</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>151422</t>
+          <t>149392</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>164037</t>
+          <t>166376</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>214309</t>
+          <t>215766</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>186283</t>
+          <t>185721</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>210403</t>
+          <t>211318</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>248747</t>
+          <t>250777</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>289109</t>
+          <t>291964</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>442858</t>
+          <t>441401</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>493130</t>
+          <t>490791</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,68%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>287743</t>
+          <t>289786</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>357414</t>
+          <t>359789</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>606242</t>
+          <t>604553</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>705030</t>
+          <t>701740</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>915013</t>
+          <t>920510</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1032720</t>
+          <t>1034593</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3036936</t>
+          <t>3034561</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3106607</t>
+          <t>3104564</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2839512</t>
+          <t>2842802</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2938300</t>
+          <t>2939989</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5906172</t>
+          <t>5904299</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6023879</t>
+          <t>6018382</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,73%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>31291</t>
+          <t>33334</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15509</t>
+          <t>17931</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55506</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>75647</t>
+          <t>89779</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57839</t>
+          <t>67158</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96444</t>
+          <t>114759</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>106938</t>
+          <t>123113</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81909</t>
+          <t>96231</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139183</t>
+          <t>159960</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>368696</t>
+          <t>374459</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>344481</t>
+          <t>350823</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>384478</t>
+          <t>389862</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>237553</t>
+          <t>272733</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>216756</t>
+          <t>247753</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>255361</t>
+          <t>295354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>606249</t>
+          <t>647192</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>574004</t>
+          <t>610345</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>631278</t>
+          <t>674074</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42134</t>
+          <t>47926</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29543</t>
+          <t>33543</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59021</t>
+          <t>67284</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>187493</t>
+          <t>128614</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131363</t>
+          <t>109559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>322075</t>
+          <t>150754</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>229627</t>
+          <t>176539</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>165130</t>
+          <t>150849</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>407097</t>
+          <t>205292</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>381413</t>
+          <t>428964</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>364526</t>
+          <t>409606</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>394004</t>
+          <t>443347</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>324600</t>
+          <t>373119</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>190018</t>
+          <t>350979</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>380730</t>
+          <t>392174</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>706013</t>
+          <t>802084</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>528543</t>
+          <t>773331</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>770510</t>
+          <t>827774</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>84,59%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>77805</t>
+          <t>85519</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62051</t>
+          <t>67559</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95512</t>
+          <t>104393</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>165730</t>
+          <t>192323</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>123024</t>
+          <t>172793</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>188699</t>
+          <t>212021</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>243535</t>
+          <t>277841</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>206969</t>
+          <t>252856</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>269040</t>
+          <t>304928</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>458533</t>
+          <t>535318</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>440826</t>
+          <t>516444</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>474287</t>
+          <t>553278</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>426272</t>
+          <t>430870</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>403303</t>
+          <t>411172</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>468978</t>
+          <t>450400</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>884805</t>
+          <t>966188</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>859300</t>
+          <t>939101</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>921371</t>
+          <t>991173</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>79,67%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>153286</t>
+          <t>163571</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68203</t>
+          <t>140088</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>221758</t>
+          <t>187798</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>253438</t>
+          <t>276660</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>218369</t>
+          <t>255840</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>279185</t>
+          <t>297639</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>406724</t>
+          <t>440231</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>259605</t>
+          <t>410151</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>498870</t>
+          <t>475139</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>734500</t>
+          <t>537046</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>666028</t>
+          <t>512819</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>819583</t>
+          <t>560529</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>459443</t>
+          <t>460226</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>433696</t>
+          <t>439247</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>494512</t>
+          <t>481046</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1193943</t>
+          <t>997273</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1101797</t>
+          <t>962365</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1341062</t>
+          <t>1027353</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>71,47%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>167079</t>
+          <t>176325</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>147251</t>
+          <t>155085</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>187554</t>
+          <t>197464</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>240890</t>
+          <t>269048</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>223517</t>
+          <t>250549</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>257382</t>
+          <t>286698</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>407969</t>
+          <t>445374</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>378992</t>
+          <t>416918</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>436479</t>
+          <t>476026</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,08%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>394155</t>
+          <t>433021</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>373680</t>
+          <t>411882</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>413983</t>
+          <t>454261</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>307015</t>
+          <t>339807</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>290523</t>
+          <t>322157</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>324388</t>
+          <t>358306</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>701170</t>
+          <t>772828</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>672660</t>
+          <t>742176</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>730147</t>
+          <t>801284</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,78%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>109663</t>
+          <t>120491</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96093</t>
+          <t>104633</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123490</t>
+          <t>136736</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>397289</t>
+          <t>214886</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>284612</t>
+          <t>200058</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>512487</t>
+          <t>230097</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>506952</t>
+          <t>335377</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>375525</t>
+          <t>314935</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>725401</t>
+          <t>359231</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>42,45%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>258502</t>
+          <t>286589</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244675</t>
+          <t>270344</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>272072</t>
+          <t>302447</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>211079</t>
+          <t>224280</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>95881</t>
+          <t>209069</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>323756</t>
+          <t>239108</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>469581</t>
+          <t>510869</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>251132</t>
+          <t>487015</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>601008</t>
+          <t>531311</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>62,78%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>117431</t>
+          <t>130245</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105330</t>
+          <t>116181</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>130219</t>
+          <t>144857</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>251686</t>
+          <t>277555</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>236937</t>
+          <t>262050</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>266323</t>
+          <t>292441</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>369117</t>
+          <t>407800</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>349451</t>
+          <t>384771</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>387659</t>
+          <t>428276</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>55,28%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>165328</t>
+          <t>179953</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>152540</t>
+          <t>165341</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>177429</t>
+          <t>194017</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>174145</t>
+          <t>187054</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>159508</t>
+          <t>172168</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>188894</t>
+          <t>202559</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>339473</t>
+          <t>367007</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>320931</t>
+          <t>346531</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>359139</t>
+          <t>390036</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,34%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>698690</t>
+          <t>757410</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>541691</t>
+          <t>706662</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>774077</t>
+          <t>812902</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1572173</t>
+          <t>1448866</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1405779</t>
+          <t>1396088</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1954309</t>
+          <t>1501379</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2270863</t>
+          <t>2206276</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2046408</t>
+          <t>2131668</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2721471</t>
+          <t>2284908</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2761127</t>
+          <t>2775352</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2685740</t>
+          <t>2719860</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2918126</t>
+          <t>2826100</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2140107</t>
+          <t>2288088</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1757971</t>
+          <t>2235575</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2306501</t>
+          <t>2340866</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4901234</t>
+          <t>5063440</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4450626</t>
+          <t>4984808</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5125689</t>
+          <t>5138048</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
